--- a/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_6807_SW2.xlsx
+++ b/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_6807_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS2"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1000,6 +1000,946 @@
       <c r="BS2" t="inlineStr">
         <is>
           <t>6807-06-06-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6807-04-04-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="H3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="J3" t="n">
+        <v>75</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0.12594</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.12594</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>6807-04-04-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>90 deg Adjustable Male ORB x Adjustable Male ORB Elbow, 7/16-20 (adjustable male ORB) x 7/16-20 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>7/16-20 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>7/16-20 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, M7_1@DRIVE, M7_2@DRIVE, C4_1HEX@HEX, C4_2HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing; end-library values (Q-TRANSFER-ENDLIB, user 2026-10-08 'reuse end details - yes'): adjustable ORB tip-to-body-face = Air-Way 6801 ORB_I3 of the same ORB size (= the Brennan 6801 STEPs); adjustable ORB thread length = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); adjustable ORB O-ring undercut dia = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); two adjustable ORB legs on one 90 deg elbow forging (OMi "MAORB - MAORB 90 deg Elbow Forged"; no Brennan 6807 STEP seen: the body form - 2500HX hex arms + 30deg corner puck, each ORB leg = the ORB leg of the accepted 6801 forging - is ASSUMED from the Brennan 6801-XX-XX-NWO-FG STEPs, shape only)</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-04-04-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, M7_1@DRIVE=M1, M7_2@DRIVE=M2, C4_1HEX@HEX=C, C4_2HEX@HEX=C2; user 2026-10-21 "yes you can use them following my rule") | leg 1: adjustable ORB tip-to-body-face 0.73 = Air-Way 6801 ORB_I3 for -04 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 1: adjustable ORB thread length 0.265 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -04 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 1: adjustable ORB undercut dia 0.364 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -04 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB tip-to-body-face 0.73 = Air-Way 6801 ORB_I3 for -04 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 2: adjustable ORB thread length 0.265 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -04 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB undercut dia 0.364 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -04 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: its revolved locknut envelope (radius 0.3351, 0.01 beyond the nut corners) reaches past leg 1's locknut slab start 0.3290: NUTCUT1 removes 0.000131 in^3 of it (0.63 % of NUTCUT2); the finished solid is unchanged; leg 1: the adjustable ORB body face is a -0.0062 step (hex flats radius 0.2190 vs neck radius 0.2252); leg 2: the adjustable ORB body face is a -0.0062 step (hex flats radius 0.2190 vs neck radius 0.2252)</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>6807-04-04-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6807-08-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="H4" t="n">
+        <v>75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.51518</v>
+      </c>
+      <c r="J4" t="n">
+        <v>75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.40722</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>6807-08-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>90 deg Adjustable Male ORB x Adjustable Male ORB Elbow, 3/4-16 (adjustable male ORB) x 9/16-18 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>3/4-16 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>9/16-18 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, M7_1@DRIVE, M7_2@DRIVE, C4_1HEX@HEX, C4_2HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-08-06 NWO (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing; end-library values (Q-TRANSFER-ENDLIB, user 2026-10-08 'reuse end details - yes'): adjustable ORB tip-to-body-face = Air-Way 6801 ORB_I3 of the same ORB size (= the Brennan 6801 STEPs); adjustable ORB thread length = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); adjustable ORB O-ring undercut dia = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); two adjustable ORB legs on one 90 deg elbow forging (OMi "MAORB - MAORB 90 deg Elbow Forged"; no Brennan 6807 STEP seen: the body form - 2500HX hex arms + 30deg corner puck, each ORB leg = the ORB leg of the accepted 6801 forging - is ASSUMED from the Brennan 6801-XX-XX-NWO-FG STEPs, shape only)</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-08-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-08-06-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, M7_1@DRIVE=M1, M7_2@DRIVE=M2, C4_1HEX@HEX=C, C4_2HEX@HEX=C2; user 2026-10-21 "yes you can use them following my rule") | leg 1: adjustable ORB tip-to-body-face 0.86 = Air-Way 6801 ORB_I3 for -08 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 1: adjustable ORB thread length 0.344 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -08 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 1: adjustable ORB undercut dia 0.66 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -08 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB tip-to-body-face 0.75 = Air-Way 6801 ORB_I3 for -06 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 2: adjustable ORB thread length 0.312 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -06 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB undercut dia 0.481 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -06 (end library, Q-TRANSFER-ENDLIB 2026-10-08)</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>6807-08-06-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6807-08-08-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="H5" t="n">
+        <v>75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.51518</v>
+      </c>
+      <c r="J5" t="n">
+        <v>75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.51518</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>6807-08-08-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>90 deg Adjustable Male ORB x Adjustable Male ORB Elbow, 3/4-16 (adjustable male ORB) x 3/4-16 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>3/4-16 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>3/4-16 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, M7_1@DRIVE, M7_2@DRIVE, C4_1HEX@HEX, C4_2HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-08-08 NWO (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing; end-library values (Q-TRANSFER-ENDLIB, user 2026-10-08 'reuse end details - yes'): adjustable ORB tip-to-body-face = Air-Way 6801 ORB_I3 of the same ORB size (= the Brennan 6801 STEPs); adjustable ORB thread length = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); adjustable ORB O-ring undercut dia = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); two adjustable ORB legs on one 90 deg elbow forging (OMi "MAORB - MAORB 90 deg Elbow Forged"; no Brennan 6807 STEP seen: the body form - 2500HX hex arms + 30deg corner puck, each ORB leg = the ORB leg of the accepted 6801 forging - is ASSUMED from the Brennan 6801-XX-XX-NWO-FG STEPs, shape only)</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-08-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-08-08-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, M7_1@DRIVE=M1, M7_2@DRIVE=M2, C4_1HEX@HEX=C, C4_2HEX@HEX=C2; user 2026-10-21 "yes you can use them following my rule") | leg 1: adjustable ORB tip-to-body-face 0.86 = Air-Way 6801 ORB_I3 for -08 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 1: adjustable ORB thread length 0.344 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -08 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 1: adjustable ORB undercut dia 0.66 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -08 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB tip-to-body-face 0.86 = Air-Way 6801 ORB_I3 for -08 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 2: adjustable ORB thread length 0.344 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -08 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB undercut dia 0.66 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -08 (end library, Q-TRANSFER-ENDLIB 2026-10-08)</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>6807-08-08-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6807-12-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H6" t="n">
+        <v>75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.73169</v>
+      </c>
+      <c r="J6" t="n">
+        <v>75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.73169</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.61265</v>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>6807-12-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>90 deg Adjustable Male ORB x Adjustable Male ORB Elbow, 1 1/16-12 (adjustable male ORB) x 1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, D1@BORE, D2@BORE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, M7_1@DRIVE, M7_2@DRIVE, C4_1HEX@HEX, C4_2HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6807-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing; end-library values (Q-TRANSFER-ENDLIB, user 2026-10-08 'reuse end details - yes'): adjustable ORB tip-to-body-face = Air-Way 6801 ORB_I3 of the same ORB size (= the Brennan 6801 STEPs); adjustable ORB thread length = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); adjustable ORB O-ring undercut dia = the ORB end library (6401 / 6405 / 6410 tables, = Air-Way 6801 at every dash); two adjustable ORB legs on one 90 deg elbow forging (OMi "MAORB - MAORB 90 deg Elbow Forged"; no Brennan 6807 STEP seen: the body form - 2500HX hex arms + 30deg corner puck, each ORB leg = the ORB leg of the accepted 6801 forging - is ASSUMED from the Brennan 6801-XX-XX-NWO-FG STEPs, shape only)</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6807-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6807-12-12-NWO-FG (PARTcommunity / CADENAS, Y@HEX=Y, D1@BORE=B1D, D2@BORE=B2D, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, M7_1@DRIVE=M1, M7_2@DRIVE=M2, C4_1HEX@HEX=C, C4_2HEX@HEX=C2; user 2026-10-21 "yes you can use them following my rule") | leg 1: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -12 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 1: adjustable ORB thread length 0.469 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -12 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 1: adjustable ORB undercut dia 0.945 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -12 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB tip-to-body-face 1.14 = Air-Way 6801 ORB_I3 for -12 (= Brennan 6801 STEP; not printed for this series - ASSUMPTION); leg 2: adjustable ORB thread length 0.469 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_THDL at every dash -02..-32) for -12 (end library, Q-TRANSFER-ENDLIB 2026-10-08); leg 2: adjustable ORB undercut dia 0.945 = the ORB end library (6401 / 6405 / 6410 tables; = Air-Way 6801 ORB_GRVDIA at every dash -02..-32) for -12 (end library, Q-TRANSFER-ENDLIB 2026-10-08)</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>6807-12-12-NWO-FG</t>
         </is>
       </c>
     </row>
